--- a/用卷/xlsx/常规科目/1988.xlsx
+++ b/用卷/xlsx/常规科目/1988.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\常规科目\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA930CF-BCB3-43AA-946A-798BA64CBB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32714234-139D-4EDD-96F6-E196E95BEB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -955,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
